--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/107.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/107.xlsx
@@ -426,13 +426,13 @@
         <v>-41.20011033858944</v>
       </c>
       <c r="E2">
-        <v>-11.5155743429904</v>
+        <v>-12.0798794721175</v>
       </c>
       <c r="F2">
-        <v>0.335893722546261</v>
+        <v>0.1961282608763172</v>
       </c>
       <c r="G2">
-        <v>-18.57448646759241</v>
+        <v>-20.36319113079104</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-40.28222900220631</v>
       </c>
       <c r="E3">
-        <v>-11.06409119950226</v>
+        <v>-13.0324475619462</v>
       </c>
       <c r="F3">
-        <v>-0.3958023759791395</v>
+        <v>0.3578388317812255</v>
       </c>
       <c r="G3">
-        <v>-18.30335803106071</v>
+        <v>-19.68851011251874</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-39.00533510581702</v>
       </c>
       <c r="E4">
-        <v>-11.38427056695594</v>
+        <v>-13.91533307216693</v>
       </c>
       <c r="F4">
-        <v>0.2323908723012683</v>
+        <v>-0.179877643663212</v>
       </c>
       <c r="G4">
-        <v>-16.6193520581995</v>
+        <v>-19.32633587448884</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-37.55988373177452</v>
       </c>
       <c r="E5">
-        <v>-12.27741866236032</v>
+        <v>-14.74065922663685</v>
       </c>
       <c r="F5">
-        <v>-0.03528362840234989</v>
+        <v>0.4571203217415518</v>
       </c>
       <c r="G5">
-        <v>-16.57733604012242</v>
+        <v>-19.01353538547994</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-35.98361660283707</v>
       </c>
       <c r="E6">
-        <v>-13.69105966062618</v>
+        <v>-15.70585723210436</v>
       </c>
       <c r="F6">
-        <v>-0.2657462086374088</v>
+        <v>0.9099689000343744</v>
       </c>
       <c r="G6">
-        <v>-16.26433387109385</v>
+        <v>-18.44143509099551</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-34.39036900684924</v>
       </c>
       <c r="E7">
-        <v>-14.29082490804467</v>
+        <v>-16.52869976620204</v>
       </c>
       <c r="F7">
-        <v>0.5919545122626302</v>
+        <v>0.274278926758631</v>
       </c>
       <c r="G7">
-        <v>-16.35144266974864</v>
+        <v>-18.07899455701732</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-32.8487071110228</v>
       </c>
       <c r="E8">
-        <v>-14.57473428099863</v>
+        <v>-16.59645525575529</v>
       </c>
       <c r="F8">
-        <v>0.2842541270231426</v>
+        <v>0.8777139301041672</v>
       </c>
       <c r="G8">
-        <v>-15.29982691621443</v>
+        <v>-16.96159065053165</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-31.40089898850192</v>
       </c>
       <c r="E9">
-        <v>-14.7038493146649</v>
+        <v>-17.7662985960424</v>
       </c>
       <c r="F9">
-        <v>0.2054888125279516</v>
+        <v>0.6518786101811463</v>
       </c>
       <c r="G9">
-        <v>-15.33965251957957</v>
+        <v>-16.3419056197573</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-30.10592847333316</v>
       </c>
       <c r="E10">
-        <v>-15.31235707192215</v>
+        <v>-18.25339552664094</v>
       </c>
       <c r="F10">
-        <v>0.6642552475463738</v>
+        <v>0.7670639259078205</v>
       </c>
       <c r="G10">
-        <v>-13.73730933215608</v>
+        <v>-15.60798484865419</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-28.95485347490572</v>
       </c>
       <c r="E11">
-        <v>-16.69937598559587</v>
+        <v>-19.34165318366311</v>
       </c>
       <c r="F11">
-        <v>0.03056081134397441</v>
+        <v>0.9726879095699361</v>
       </c>
       <c r="G11">
-        <v>-13.20158323668734</v>
+        <v>-15.0901345214008</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-27.98973118283167</v>
       </c>
       <c r="E12">
-        <v>-16.78744067852753</v>
+        <v>-19.65021601904125</v>
       </c>
       <c r="F12">
-        <v>1.104893690321932</v>
+        <v>1.140677505388065</v>
       </c>
       <c r="G12">
-        <v>-13.78312267824094</v>
+        <v>-14.0420732966274</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-27.17433514947371</v>
       </c>
       <c r="E13">
-        <v>-18.30018560542645</v>
+        <v>-20.6572742414517</v>
       </c>
       <c r="F13">
-        <v>0.5676576679711178</v>
+        <v>1.178462656099361</v>
       </c>
       <c r="G13">
-        <v>-11.75007059652625</v>
+        <v>-13.64310583507494</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-26.51443272125912</v>
       </c>
       <c r="E14">
-        <v>-18.50773818817344</v>
+        <v>-22.08899832182587</v>
       </c>
       <c r="F14">
-        <v>1.348463527971487</v>
+        <v>1.566156824692392</v>
       </c>
       <c r="G14">
-        <v>-10.87028752511764</v>
+        <v>-12.47462009991955</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-25.96061462869479</v>
       </c>
       <c r="E15">
-        <v>-19.34019955969942</v>
+        <v>-22.8553613351172</v>
       </c>
       <c r="F15">
-        <v>1.335433308725451</v>
+        <v>1.559483496895439</v>
       </c>
       <c r="G15">
-        <v>-11.09683749775609</v>
+        <v>-12.20622119685786</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-25.45466048340942</v>
       </c>
       <c r="E16">
-        <v>-21.47861331304979</v>
+        <v>-22.78275904794787</v>
       </c>
       <c r="F16">
-        <v>1.282214016565194</v>
+        <v>1.536221283490023</v>
       </c>
       <c r="G16">
-        <v>-9.817374231521653</v>
+        <v>-11.39040006255923</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-24.95455267680047</v>
       </c>
       <c r="E17">
-        <v>-22.80666908554491</v>
+        <v>-23.946081846455</v>
       </c>
       <c r="F17">
-        <v>1.591398836190498</v>
+        <v>1.970779509529032</v>
       </c>
       <c r="G17">
-        <v>-10.0383711504148</v>
+        <v>-11.17111709749015</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-24.38700419283771</v>
       </c>
       <c r="E18">
-        <v>-23.21586423132364</v>
+        <v>-24.71873697490345</v>
       </c>
       <c r="F18">
-        <v>2.386924784938615</v>
+        <v>1.996755454546019</v>
       </c>
       <c r="G18">
-        <v>-9.437590521224699</v>
+        <v>-11.20668066031029</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-23.73524613655572</v>
       </c>
       <c r="E19">
-        <v>-23.69990855159844</v>
+        <v>-25.48086786585479</v>
       </c>
       <c r="F19">
-        <v>1.930148088421717</v>
+        <v>2.331510319160939</v>
       </c>
       <c r="G19">
-        <v>-9.628267557808952</v>
+        <v>-10.40226064764106</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-22.95027591718901</v>
       </c>
       <c r="E20">
-        <v>-24.0931844383691</v>
+        <v>-26.2193586779452</v>
       </c>
       <c r="F20">
-        <v>1.61397350465159</v>
+        <v>2.272248915164662</v>
       </c>
       <c r="G20">
-        <v>-8.02878835720192</v>
+        <v>-10.33606652390568</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-22.05247128219399</v>
       </c>
       <c r="E21">
-        <v>-25.07647383236756</v>
+        <v>-27.16420179470972</v>
       </c>
       <c r="F21">
-        <v>1.035329052569635</v>
+        <v>2.264246886053619</v>
       </c>
       <c r="G21">
-        <v>-9.389009785873263</v>
+        <v>-9.550686671539431</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-21.04799821669491</v>
       </c>
       <c r="E22">
-        <v>-23.81760225412143</v>
+        <v>-27.05867284815715</v>
       </c>
       <c r="F22">
-        <v>1.725605952587657</v>
+        <v>2.522046418948464</v>
       </c>
       <c r="G22">
-        <v>-7.626014430035623</v>
+        <v>-8.821454797721962</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-19.97792700105682</v>
       </c>
       <c r="E23">
-        <v>-24.9808170691341</v>
+        <v>-28.36265660781357</v>
       </c>
       <c r="F23">
-        <v>1.779898808901942</v>
+        <v>2.43854864148108</v>
       </c>
       <c r="G23">
-        <v>-8.459398043198668</v>
+        <v>-9.337596392640469</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-18.89689819064049</v>
       </c>
       <c r="E24">
-        <v>-25.526503351892</v>
+        <v>-27.09777533278041</v>
       </c>
       <c r="F24">
-        <v>2.099121784714371</v>
+        <v>2.479564425063294</v>
       </c>
       <c r="G24">
-        <v>-8.353279107803687</v>
+        <v>-8.852025311511603</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-17.84475674394806</v>
       </c>
       <c r="E25">
-        <v>-27.05228520913957</v>
+        <v>-28.34671658274888</v>
       </c>
       <c r="F25">
-        <v>2.178418082714757</v>
+        <v>2.542871575454844</v>
       </c>
       <c r="G25">
-        <v>-8.020212061220114</v>
+        <v>-8.727706875571972</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-16.89563034287004</v>
       </c>
       <c r="E26">
-        <v>-25.03743779912549</v>
+        <v>-28.22956279769811</v>
       </c>
       <c r="F26">
-        <v>1.69236853891773</v>
+        <v>2.320025833488526</v>
       </c>
       <c r="G26">
-        <v>-8.630611978856173</v>
+        <v>-9.094100076861105</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-16.0780047778335</v>
       </c>
       <c r="E27">
-        <v>-25.94273819086632</v>
+        <v>-28.33847453487475</v>
       </c>
       <c r="F27">
-        <v>1.889780088148491</v>
+        <v>2.040784838739619</v>
       </c>
       <c r="G27">
-        <v>-7.137392693852043</v>
+        <v>-9.139084511538282</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-15.45334711124858</v>
       </c>
       <c r="E28">
-        <v>-25.06410972225354</v>
+        <v>-27.82757762677928</v>
       </c>
       <c r="F28">
-        <v>1.353985425078549</v>
+        <v>1.842922657641734</v>
       </c>
       <c r="G28">
-        <v>-8.019176900989738</v>
+        <v>-8.767180028417309</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-15.03279659797789</v>
       </c>
       <c r="E29">
-        <v>-23.17711892287432</v>
+        <v>-27.82673452488034</v>
       </c>
       <c r="F29">
-        <v>1.144825969341285</v>
+        <v>1.697825823367373</v>
       </c>
       <c r="G29">
-        <v>-9.549360413287145</v>
+        <v>-8.744800725782286</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-14.8403228084578</v>
       </c>
       <c r="E30">
-        <v>-24.88744457212931</v>
+        <v>-27.35881297096853</v>
       </c>
       <c r="F30">
-        <v>1.941784993696244</v>
+        <v>1.733583130676617</v>
       </c>
       <c r="G30">
-        <v>-7.802290599455296</v>
+        <v>-8.065354445945053</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-14.88011956690417</v>
       </c>
       <c r="E31">
-        <v>-22.95392119306671</v>
+        <v>-26.76864994813305</v>
       </c>
       <c r="F31">
-        <v>1.651442219015018</v>
+        <v>1.601281259305896</v>
       </c>
       <c r="G31">
-        <v>-7.559116710632936</v>
+        <v>-8.479754018775578</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-15.1287071355059</v>
       </c>
       <c r="E32">
-        <v>-24.461441380119</v>
+        <v>-26.72159406382274</v>
       </c>
       <c r="F32">
-        <v>2.148414615385358</v>
+        <v>1.36528601318754</v>
       </c>
       <c r="G32">
-        <v>-7.994599351408997</v>
+        <v>-8.89999774337331</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-15.58570568467021</v>
       </c>
       <c r="E33">
-        <v>-22.0325312606535</v>
+        <v>-26.07868110395061</v>
       </c>
       <c r="F33">
-        <v>1.593226214681074</v>
+        <v>1.472596040015798</v>
       </c>
       <c r="G33">
-        <v>-8.344089286842967</v>
+        <v>-8.901853982777592</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-16.19999765836184</v>
       </c>
       <c r="E34">
-        <v>-23.5936984783886</v>
+        <v>-24.83604858198456</v>
       </c>
       <c r="F34">
-        <v>1.121169453052136</v>
+        <v>1.832680723073521</v>
       </c>
       <c r="G34">
-        <v>-7.724062248527178</v>
+        <v>-8.222469055438252</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-16.95542979470193</v>
       </c>
       <c r="E35">
-        <v>-23.8412838650956</v>
+        <v>-25.17884218510193</v>
       </c>
       <c r="F35">
-        <v>1.27242768406852</v>
+        <v>1.416986079531062</v>
       </c>
       <c r="G35">
-        <v>-8.817010005055593</v>
+        <v>-8.546240545905166</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-17.79288931690285</v>
       </c>
       <c r="E36">
-        <v>-22.46138355563264</v>
+        <v>-23.78596724346021</v>
       </c>
       <c r="F36">
-        <v>1.863172927170571</v>
+        <v>1.510861643820719</v>
       </c>
       <c r="G36">
-        <v>-9.375700209947768</v>
+        <v>-9.379564111942615</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-18.68279692303233</v>
       </c>
       <c r="E37">
-        <v>-20.17864155553315</v>
+        <v>-23.3816770402561</v>
       </c>
       <c r="F37">
-        <v>1.783699358545987</v>
+        <v>2.116328632405323</v>
       </c>
       <c r="G37">
-        <v>-8.514240649451889</v>
+        <v>-9.560315097591456</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-19.58384703263942</v>
       </c>
       <c r="E38">
-        <v>-19.59072126681308</v>
+        <v>-22.89037705979683</v>
       </c>
       <c r="F38">
-        <v>1.254072719157289</v>
+        <v>1.891690303379347</v>
       </c>
       <c r="G38">
-        <v>-7.98958933253865</v>
+        <v>-9.188114294959391</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-20.45255398692314</v>
       </c>
       <c r="E39">
-        <v>-20.28474779845988</v>
+        <v>-22.37885094018565</v>
       </c>
       <c r="F39">
-        <v>1.827529934562914</v>
+        <v>1.885906642173001</v>
       </c>
       <c r="G39">
-        <v>-8.244392783142125</v>
+        <v>-9.513851676103414</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-21.2760357026986</v>
       </c>
       <c r="E40">
-        <v>-18.65282231938367</v>
+        <v>-21.652682706096</v>
       </c>
       <c r="F40">
-        <v>2.230111522119057</v>
+        <v>2.149385461981439</v>
       </c>
       <c r="G40">
-        <v>-9.642502642691998</v>
+        <v>-9.47842256662971</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-22.01318358142969</v>
       </c>
       <c r="E41">
-        <v>-18.13674428016048</v>
+        <v>-21.25571876766889</v>
       </c>
       <c r="F41">
-        <v>1.983587726311118</v>
+        <v>2.077372170186467</v>
       </c>
       <c r="G41">
-        <v>-9.843565221259702</v>
+        <v>-10.51321598739108</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-22.67039371157822</v>
       </c>
       <c r="E42">
-        <v>-17.28423535756955</v>
+        <v>-20.90551998875935</v>
       </c>
       <c r="F42">
-        <v>2.278720121315332</v>
+        <v>2.198552380807201</v>
       </c>
       <c r="G42">
-        <v>-9.698463953002511</v>
+        <v>-10.17648998226306</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-23.22275596619939</v>
       </c>
       <c r="E43">
-        <v>-16.9371141082517</v>
+        <v>-19.30078143101547</v>
       </c>
       <c r="F43">
-        <v>2.200164383773049</v>
+        <v>2.406025280512365</v>
       </c>
       <c r="G43">
-        <v>-10.40927180224049</v>
+        <v>-10.24476095332067</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-23.68551954810582</v>
       </c>
       <c r="E44">
-        <v>-17.2271370082758</v>
+        <v>-20.24983590406337</v>
       </c>
       <c r="F44">
-        <v>2.53500539859786</v>
+        <v>2.269717424381707</v>
       </c>
       <c r="G44">
-        <v>-10.57658920159576</v>
+        <v>-10.52818469150422</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-24.05709113982288</v>
       </c>
       <c r="E45">
-        <v>-15.33370042492045</v>
+        <v>-19.1062117868699</v>
       </c>
       <c r="F45">
-        <v>2.013178666673922</v>
+        <v>2.387900601739112</v>
       </c>
       <c r="G45">
-        <v>-8.666045004446763</v>
+        <v>-10.48949606740852</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-24.34758043013951</v>
       </c>
       <c r="E46">
-        <v>-17.55128684575602</v>
+        <v>-18.05253376733825</v>
       </c>
       <c r="F46">
-        <v>1.967253977862718</v>
+        <v>2.591097468911026</v>
       </c>
       <c r="G46">
-        <v>-10.44492413037674</v>
+        <v>-11.22704707886557</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-24.57946123067375</v>
       </c>
       <c r="E47">
-        <v>-14.88649924230821</v>
+        <v>-17.3490129946029</v>
       </c>
       <c r="F47">
-        <v>1.825114415216351</v>
+        <v>2.904881384356673</v>
       </c>
       <c r="G47">
-        <v>-10.43913219350135</v>
+        <v>-11.99881711967834</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-24.74632924615345</v>
       </c>
       <c r="E48">
-        <v>-14.87542262770489</v>
+        <v>-17.70875169992557</v>
       </c>
       <c r="F48">
-        <v>2.008629272897748</v>
+        <v>2.619172496926706</v>
       </c>
       <c r="G48">
-        <v>-11.25186481694869</v>
+        <v>-11.85203844802136</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-24.88046436633561</v>
       </c>
       <c r="E49">
-        <v>-13.66852848918899</v>
+        <v>-17.39090643723644</v>
       </c>
       <c r="F49">
-        <v>2.147674054927255</v>
+        <v>2.98357463088782</v>
       </c>
       <c r="G49">
-        <v>-10.89070876930933</v>
+        <v>-11.94405675187974</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-24.967502469935</v>
       </c>
       <c r="E50">
-        <v>-12.37306296595979</v>
+        <v>-16.44837250596853</v>
       </c>
       <c r="F50">
-        <v>1.885242291515955</v>
+        <v>2.696702715624323</v>
       </c>
       <c r="G50">
-        <v>-11.36347153747419</v>
+        <v>-11.87160858947634</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-25.03501696905595</v>
       </c>
       <c r="E51">
-        <v>-14.7245073877946</v>
+        <v>-16.06166284630242</v>
       </c>
       <c r="F51">
-        <v>2.346278453218048</v>
+        <v>2.20511802084179</v>
       </c>
       <c r="G51">
-        <v>-11.33322606138614</v>
+        <v>-12.28169129612546</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-25.06872966871792</v>
       </c>
       <c r="E52">
-        <v>-13.29556595900806</v>
+        <v>-15.35197870796102</v>
       </c>
       <c r="F52">
-        <v>2.206400333581324</v>
+        <v>2.520750852330486</v>
       </c>
       <c r="G52">
-        <v>-11.32885828568521</v>
+        <v>-12.26097634316728</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-25.0826195586529</v>
       </c>
       <c r="E53">
-        <v>-11.90232553476975</v>
+        <v>-14.47532716793886</v>
       </c>
       <c r="F53">
-        <v>1.760887777007694</v>
+        <v>2.419786119807671</v>
       </c>
       <c r="G53">
-        <v>-11.62107631702393</v>
+        <v>-12.64549986026939</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-25.07812358571011</v>
       </c>
       <c r="E54">
-        <v>-10.99122310680814</v>
+        <v>-14.54735631194536</v>
       </c>
       <c r="F54">
-        <v>2.371522121450961</v>
+        <v>2.486542592064477</v>
       </c>
       <c r="G54">
-        <v>-11.54524201888586</v>
+        <v>-12.70902710840496</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-25.04242153625601</v>
       </c>
       <c r="E55">
-        <v>-11.61994869679466</v>
+        <v>-14.40233863211632</v>
       </c>
       <c r="F55">
-        <v>1.609970833361263</v>
+        <v>2.334267125877456</v>
       </c>
       <c r="G55">
-        <v>-11.9127500081154</v>
+        <v>-12.57946368658178</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-24.99514085172397</v>
       </c>
       <c r="E56">
-        <v>-12.17147854788659</v>
+        <v>-13.0522874524449</v>
       </c>
       <c r="F56">
-        <v>2.378510228860977</v>
+        <v>2.288754964032845</v>
       </c>
       <c r="G56">
-        <v>-12.25444164945572</v>
+        <v>-13.41375453349023</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-24.91296206975529</v>
       </c>
       <c r="E57">
-        <v>-11.16724866238835</v>
+        <v>-13.6689978020687</v>
       </c>
       <c r="F57">
-        <v>2.45298874204668</v>
+        <v>2.465550105342732</v>
       </c>
       <c r="G57">
-        <v>-11.75297896600075</v>
+        <v>-13.21753880225593</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-24.81929721285745</v>
       </c>
       <c r="E58">
-        <v>-11.0605858891441</v>
+        <v>-13.21821655129446</v>
       </c>
       <c r="F58">
-        <v>2.182235199706857</v>
+        <v>2.273146865429297</v>
       </c>
       <c r="G58">
-        <v>-12.23381546181363</v>
+        <v>-13.32529336913725</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-24.69083825587235</v>
       </c>
       <c r="E59">
-        <v>-11.24626766105454</v>
+        <v>-12.58145034418307</v>
       </c>
       <c r="F59">
-        <v>1.899051176120623</v>
+        <v>2.342226079883553</v>
       </c>
       <c r="G59">
-        <v>-12.92360029023167</v>
+        <v>-13.40863355797476</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-24.54657893652055</v>
       </c>
       <c r="E60">
-        <v>-10.41873615137113</v>
+        <v>-12.09316974835695</v>
       </c>
       <c r="F60">
-        <v>2.468353300633806</v>
+        <v>2.656392701069294</v>
       </c>
       <c r="G60">
-        <v>-13.76902335207663</v>
+        <v>-13.21006162974698</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-24.37976671487368</v>
       </c>
       <c r="E61">
-        <v>-11.49830944351308</v>
+        <v>-11.22380294099854</v>
       </c>
       <c r="F61">
-        <v>2.276365901156576</v>
+        <v>2.340743302232542</v>
       </c>
       <c r="G61">
-        <v>-12.92612618562357</v>
+        <v>-13.79333330033679</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-24.19201294954943</v>
       </c>
       <c r="E62">
-        <v>-10.89800012541104</v>
+        <v>-12.25985473166762</v>
       </c>
       <c r="F62">
-        <v>2.592851951070155</v>
+        <v>2.025518027506024</v>
       </c>
       <c r="G62">
-        <v>-12.80329326335628</v>
+        <v>-13.46397742718948</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-24.00091118257584</v>
       </c>
       <c r="E63">
-        <v>-9.639514795818121</v>
+        <v>-10.98766380470276</v>
       </c>
       <c r="F63">
-        <v>2.133696183372417</v>
+        <v>2.147225079794938</v>
       </c>
       <c r="G63">
-        <v>-12.54167576937</v>
+        <v>-13.74433876196766</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-23.79401344459219</v>
       </c>
       <c r="E64">
-        <v>-8.305789889864606</v>
+        <v>-11.65810009602454</v>
       </c>
       <c r="F64">
-        <v>1.530305083499229</v>
+        <v>2.106905124831075</v>
       </c>
       <c r="G64">
-        <v>-12.35259520310321</v>
+        <v>-13.6532551046729</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-23.60191886019105</v>
       </c>
       <c r="E65">
-        <v>-8.083543245450381</v>
+        <v>-11.12370639485885</v>
       </c>
       <c r="F65">
-        <v>2.210644888153269</v>
+        <v>2.47178108494659</v>
       </c>
       <c r="G65">
-        <v>-12.98807784939839</v>
+        <v>-13.38916262481424</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-23.40790352330858</v>
       </c>
       <c r="E66">
-        <v>-8.306948635824233</v>
+        <v>-11.35106564241394</v>
       </c>
       <c r="F66">
-        <v>1.687913579025474</v>
+        <v>2.464945397138689</v>
       </c>
       <c r="G66">
-        <v>-13.6236701469664</v>
+        <v>-13.21838859962034</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-23.23954112368837</v>
       </c>
       <c r="E67">
-        <v>-10.01481973718625</v>
+        <v>-11.76839692917801</v>
       </c>
       <c r="F67">
-        <v>1.556247893820104</v>
+        <v>1.979427665214259</v>
       </c>
       <c r="G67">
-        <v>-13.73775707485346</v>
+        <v>-13.06778779788197</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-23.08472781619668</v>
       </c>
       <c r="E68">
-        <v>-8.759931088600633</v>
+        <v>-10.85628942407579</v>
       </c>
       <c r="F68">
-        <v>1.763618075967321</v>
+        <v>2.265893680450384</v>
       </c>
       <c r="G68">
-        <v>-13.23102982493051</v>
+        <v>-13.83502297533998</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-22.95398263043286</v>
       </c>
       <c r="E69">
-        <v>-8.135097057625478</v>
+        <v>-11.24562391329919</v>
       </c>
       <c r="F69">
-        <v>1.78480108719171</v>
+        <v>2.191506287678989</v>
       </c>
       <c r="G69">
-        <v>-11.92978250582783</v>
+        <v>-13.59959516571945</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-22.8523777549762</v>
       </c>
       <c r="E70">
-        <v>-10.85622712590592</v>
+        <v>-11.40087095262128</v>
       </c>
       <c r="F70">
-        <v>2.387516239264214</v>
+        <v>2.005259474303159</v>
       </c>
       <c r="G70">
-        <v>-12.11961366116456</v>
+        <v>-12.87663038429295</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-22.76351224909728</v>
       </c>
       <c r="E71">
-        <v>-10.87466738418815</v>
+        <v>-11.55164083013521</v>
       </c>
       <c r="F71">
-        <v>2.310973434510733</v>
+        <v>2.008509987991745</v>
       </c>
       <c r="G71">
-        <v>-12.06775513597898</v>
+        <v>-12.93859510179073</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-22.70442874902225</v>
       </c>
       <c r="E72">
-        <v>-8.617147836464353</v>
+        <v>-11.5983270786376</v>
       </c>
       <c r="F72">
-        <v>1.889581279971819</v>
+        <v>1.815043124333114</v>
       </c>
       <c r="G72">
-        <v>-11.95044524389419</v>
+        <v>-12.59592312585645</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-22.64631519630881</v>
       </c>
       <c r="E73">
-        <v>-10.53515066480607</v>
+        <v>-11.94686041980589</v>
       </c>
       <c r="F73">
-        <v>1.367603785180572</v>
+        <v>1.908837508617297</v>
       </c>
       <c r="G73">
-        <v>-14.06326862659035</v>
+        <v>-12.59296384686242</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-22.60492089202069</v>
       </c>
       <c r="E74">
-        <v>-10.74187260528809</v>
+        <v>-12.37847044710472</v>
       </c>
       <c r="F74">
-        <v>1.583482957289346</v>
+        <v>1.668988697341117</v>
       </c>
       <c r="G74">
-        <v>-12.06352703511367</v>
+        <v>-12.2543006692478</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-22.55146507057646</v>
       </c>
       <c r="E75">
-        <v>-10.63738611477805</v>
+        <v>-12.52262841218952</v>
       </c>
       <c r="F75">
-        <v>2.138500714308654</v>
+        <v>1.76244013752054</v>
       </c>
       <c r="G75">
-        <v>-12.69980595850914</v>
+        <v>-12.1828237038323</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-22.49429961754347</v>
       </c>
       <c r="E76">
-        <v>-10.65358363894488</v>
+        <v>-12.64199170566509</v>
       </c>
       <c r="F76">
-        <v>2.504879332892847</v>
+        <v>1.83129569277604</v>
       </c>
       <c r="G76">
-        <v>-12.22876758714671</v>
+        <v>-11.36694382778037</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-22.42255198833946</v>
       </c>
       <c r="E77">
-        <v>-10.21470964503892</v>
+        <v>-12.53319418179989</v>
       </c>
       <c r="F77">
-        <v>1.816963279972803</v>
+        <v>1.394823938036564</v>
       </c>
       <c r="G77">
-        <v>-11.42385414374976</v>
+        <v>-11.71426553983142</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-22.32348386341751</v>
       </c>
       <c r="E78">
-        <v>-11.72522429745642</v>
+        <v>-13.4338762025475</v>
       </c>
       <c r="F78">
-        <v>2.362519424517335</v>
+        <v>1.40364936434599</v>
       </c>
       <c r="G78">
-        <v>-11.68573271219515</v>
+        <v>-10.67092845739564</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-22.20751528196846</v>
       </c>
       <c r="E79">
-        <v>-11.06004181846055</v>
+        <v>-12.92813135310048</v>
       </c>
       <c r="F79">
-        <v>1.767960377892796</v>
+        <v>1.41681377911128</v>
       </c>
       <c r="G79">
-        <v>-10.97351114476108</v>
+        <v>-10.56090515346465</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-22.05343291573413</v>
       </c>
       <c r="E80">
-        <v>-11.79731573963279</v>
+        <v>-14.15175878004412</v>
       </c>
       <c r="F80">
-        <v>2.195141163842473</v>
+        <v>1.786070146052799</v>
       </c>
       <c r="G80">
-        <v>-12.68489991226618</v>
+        <v>-10.92718087124718</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-21.88137127094369</v>
       </c>
       <c r="E81">
-        <v>-12.19052517502226</v>
+        <v>-15.76116139410577</v>
       </c>
       <c r="F81">
-        <v>2.107165232195554</v>
+        <v>1.597871699075973</v>
       </c>
       <c r="G81">
-        <v>-10.53097427209983</v>
+        <v>-9.875119985760191</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-21.67023073797144</v>
       </c>
       <c r="E82">
-        <v>-11.84921011513652</v>
+        <v>-15.84849927505559</v>
       </c>
       <c r="F82">
-        <v>2.041510488584471</v>
+        <v>1.679812145826095</v>
       </c>
       <c r="G82">
-        <v>-11.2073529270425</v>
+        <v>-10.06842865289229</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-21.43855269189139</v>
       </c>
       <c r="E83">
-        <v>-13.42466437982903</v>
+        <v>-16.70038106273648</v>
       </c>
       <c r="F83">
-        <v>1.254833160433059</v>
+        <v>1.334422700494035</v>
       </c>
       <c r="G83">
-        <v>-10.58462246270262</v>
+        <v>-10.41243341394033</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-21.17793810573489</v>
       </c>
       <c r="E84">
-        <v>-16.27488040929646</v>
+        <v>-17.84727375724258</v>
       </c>
       <c r="F84">
-        <v>1.504663798912973</v>
+        <v>1.179966971302845</v>
       </c>
       <c r="G84">
-        <v>-10.09885427035712</v>
+        <v>-8.849477224790677</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-20.8948671754411</v>
       </c>
       <c r="E85">
-        <v>-17.39945374614294</v>
+        <v>-18.17293536364503</v>
       </c>
       <c r="F85">
-        <v>1.276508221894711</v>
+        <v>1.520217225267936</v>
       </c>
       <c r="G85">
-        <v>-10.10747364362468</v>
+        <v>-9.013869284831603</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-20.60200895438916</v>
       </c>
       <c r="E86">
-        <v>-17.35098576998219</v>
+        <v>-18.49323932743846</v>
       </c>
       <c r="F86">
-        <v>1.688763483980746</v>
+        <v>1.315176412257392</v>
       </c>
       <c r="G86">
-        <v>-9.937783077436093</v>
+        <v>-9.175486123372176</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-20.2914583996099</v>
       </c>
       <c r="E87">
-        <v>-18.97113274174118</v>
+        <v>-20.38925090181521</v>
       </c>
       <c r="F87">
-        <v>1.286196807037854</v>
+        <v>1.319213874978637</v>
       </c>
       <c r="G87">
-        <v>-9.455125587270912</v>
+        <v>-8.713987412745672</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-19.9906081926738</v>
       </c>
       <c r="E88">
-        <v>-20.31781151381684</v>
+        <v>-20.86391311770722</v>
       </c>
       <c r="F88">
-        <v>1.426472543027922</v>
+        <v>1.180361274186578</v>
       </c>
       <c r="G88">
-        <v>-9.690914985017308</v>
+        <v>-8.09369668922618</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-19.68872922868676</v>
       </c>
       <c r="E89">
-        <v>-20.18710164700183</v>
+        <v>-21.89552512547005</v>
       </c>
       <c r="F89">
-        <v>1.40692804252627</v>
+        <v>1.361646166819638</v>
       </c>
       <c r="G89">
-        <v>-9.558316572606959</v>
+        <v>-8.041117598533454</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-19.41533596431569</v>
       </c>
       <c r="E90">
-        <v>-22.7761056034055</v>
+        <v>-23.80392572922877</v>
       </c>
       <c r="F90">
-        <v>1.27711458683356</v>
+        <v>1.2934599324256</v>
       </c>
       <c r="G90">
-        <v>-8.692686347626777</v>
+        <v>-7.410092798627598</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-19.16262084032601</v>
       </c>
       <c r="E91">
-        <v>-24.47135094234004</v>
+        <v>-25.54888500772151</v>
       </c>
       <c r="F91">
-        <v>1.568882153447602</v>
+        <v>1.126482601573692</v>
       </c>
       <c r="G91">
-        <v>-8.111645558290084</v>
+        <v>-7.430062384005024</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-18.94810732860473</v>
       </c>
       <c r="E92">
-        <v>-25.27203194080843</v>
+        <v>-27.6314671412322</v>
       </c>
       <c r="F92">
-        <v>1.156837296681877</v>
+        <v>1.268738135656452</v>
       </c>
       <c r="G92">
-        <v>-8.923785542715239</v>
+        <v>-7.099941562692522</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-18.77542861156456</v>
       </c>
       <c r="E93">
-        <v>-26.19607577525821</v>
+        <v>-28.59185572798556</v>
       </c>
       <c r="F93">
-        <v>1.730985370501437</v>
+        <v>1.055483231479747</v>
       </c>
       <c r="G93">
-        <v>-8.307182495930695</v>
+        <v>-7.396871988018201</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-18.63313383245769</v>
       </c>
       <c r="E94">
-        <v>-29.48136561026938</v>
+        <v>-30.90664390666742</v>
       </c>
       <c r="F94">
-        <v>1.327262292664237</v>
+        <v>1.160941028795346</v>
       </c>
       <c r="G94">
-        <v>-8.806627073816735</v>
+        <v>-7.420488783589412</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-18.53062263722472</v>
       </c>
       <c r="E95">
-        <v>-30.45973137224226</v>
+        <v>-32.95130722078243</v>
       </c>
       <c r="F95">
-        <v>1.307866898295089</v>
+        <v>0.8380997441674892</v>
       </c>
       <c r="G95">
-        <v>-9.267231604420783</v>
+        <v>-7.145650478993734</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-18.43766651971884</v>
       </c>
       <c r="E96">
-        <v>-36.0759529183549</v>
+        <v>-34.76992370212101</v>
       </c>
       <c r="F96">
-        <v>0.9579413130652993</v>
+        <v>0.9653717686684109</v>
       </c>
       <c r="G96">
-        <v>-7.447342902453603</v>
+        <v>-7.302300375949713</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-18.35808744934046</v>
       </c>
       <c r="E97">
-        <v>-36.62664589736488</v>
+        <v>-37.10226335186159</v>
       </c>
       <c r="F97">
-        <v>0.5906647442164713</v>
+        <v>0.6543537719807113</v>
       </c>
       <c r="G97">
-        <v>-7.784828634257635</v>
+        <v>-7.692382168286314</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.25701294105922</v>
       </c>
       <c r="E98">
-        <v>-37.95280572889022</v>
+        <v>-38.80863099072403</v>
       </c>
       <c r="F98">
-        <v>1.034311817398997</v>
+        <v>0.3560230504342889</v>
       </c>
       <c r="G98">
-        <v>-9.40031822606967</v>
+        <v>-8.010214214808444</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-18.13449836543421</v>
       </c>
       <c r="E99">
-        <v>-42.05103891880634</v>
+        <v>-40.67328581959832</v>
       </c>
       <c r="F99">
-        <v>0.5446671590738204</v>
+        <v>0.4554080863199653</v>
       </c>
       <c r="G99">
-        <v>-9.433966807732233</v>
+        <v>-7.734301588813524</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-17.97305078008429</v>
       </c>
       <c r="E100">
-        <v>-41.377948725448</v>
+        <v>-43.80416756397501</v>
       </c>
       <c r="F100">
-        <v>0.5294434229451711</v>
+        <v>0.1142656806620588</v>
       </c>
       <c r="G100">
-        <v>-8.207936345671818</v>
+        <v>-7.934013107055327</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-17.7695524909387</v>
       </c>
       <c r="E101">
-        <v>-43.89256659041833</v>
+        <v>-45.11091736237377</v>
       </c>
       <c r="F101">
-        <v>0.2785400486786316</v>
+        <v>-0.1432256995589451</v>
       </c>
       <c r="G101">
-        <v>-8.840276960851595</v>
+        <v>-7.989440520096957</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-17.53826277446082</v>
       </c>
       <c r="E102">
-        <v>-47.34396618897168</v>
+        <v>-46.8597193996448</v>
       </c>
       <c r="F102">
-        <v>-0.205390531302034</v>
+        <v>-0.2557022538784647</v>
       </c>
       <c r="G102">
-        <v>-9.066847819446769</v>
+        <v>-8.313188513862551</v>
       </c>
     </row>
   </sheetData>
